--- a/decks/girlievault/keyword-research.xlsx
+++ b/decks/girlievault/keyword-research.xlsx
@@ -81,11 +81,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007CB342"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E8A200"/>
       </patternFill>
     </fill>
@@ -101,7 +96,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8743C"/>
+        <fgColor rgb="007CB342"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,12 +106,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E8E3E"/>
+        <fgColor rgb="00E8743C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007B2FF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E8E3E"/>
       </patternFill>
     </fill>
     <fill>
@@ -617,12 +617,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Women's Sweatpants: A Buyer's Guide to Comfort and Fit</t>
+          <t>Women's Sweatpants: Choosing Your Everyday Pair</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>womens sweatpants</t>
+          <t>sweatpants women</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>8100</v>
+        <v>18100</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Sports Bras for Larger Breasts: Choosing True Support</t>
+          <t>Your Essential Women's Sportswear Checklist</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>sports bras for large breasts</t>
+          <t>sportswear list</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -678,23 +678,23 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>3600</v>
+        <v>8100</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>44</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jogging Suits for Women: Matched and Movement-Ready</t>
+          <t>Moisture-Wicking Shirts: How to Choose Your Workout Top</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>jogging suits for women</t>
+          <t>moisture wicking shirts</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -724,19 +724,19 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>3600</v>
+        <v>6600</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -755,12 +755,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Athletic Tops in Bold, Vibrant Prints</t>
+          <t>Workout Shirts for Women: Breathable, Bright, and Built to Move</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>athletic tops</t>
+          <t>workout shirts for women</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -779,14 +779,14 @@
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1600</v>
+        <v>3600</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,38 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>What Take the Pledge Means: How Your Purchase Helps Feed Families</t>
+          <t>Running Clothes for Women in Every Season</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>take the pledge meaning</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Brand, Give-Back &amp; Community</t>
+          <t>running clothes for women</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Activewear Style &amp; Education</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Branded</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>Brand</t>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2900</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -851,22 +847,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>The Girlie Vault Story: How One Loss Became a Movement</t>
+          <t>Girlie Vault Reviews: What Women Say About Fit and Feel</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>girlie vault story</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+          <t>girlie vault reviews</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -884,7 +880,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -901,15 +897,15 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>The Story Behind Our Vibrant Patterns and Why They Turn Heads</t>
+          <t>The Girlie Vault Story: How One Loss Became a Movement</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>vibrant pattern activewear</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+          <t>girlie vault story</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -934,7 +930,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -951,15 +947,15 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Dressing for Confidence: How the Right Activewear Changes Your Day</t>
+          <t>The Story Behind Our Vibrant Patterns and Why They Turn Heads</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>confidence activewear women</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+          <t>vibrant pattern activewear</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -984,7 +980,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -1001,38 +997,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Sweatpants: A Buyer's Guide to Comfort and Fit</t>
+          <t>Dressing for Confidence: How the Right Activewear Changes Your Day</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>sweat pants</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Leggings &amp; Bottoms</t>
+          <t>confidence activewear women</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Brand, Give-Back &amp; Community</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>40500</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Branded</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Brand</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
           <t>spandex shorts</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -1093,15 +1093,15 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Women's Running Shorts: Finding Your Perfect Pair</t>
+          <t>Women's Gym Shorts: Finding the Right Length and Fit</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>running shorts women</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
+          <t>gym shorts women</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -1117,12 +1117,12 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8100</v>
+        <v>6600</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1139,15 +1139,15 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Yoga Pants for Women Who Want Comfort and Stretch</t>
+          <t>Cotton Leggings for Women Who Love Soft, Breathable Comfort</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>yoga pants for women</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
+          <t>cotton leggings for women</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -1159,18 +1159,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>8100</v>
+        <v>4400</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>20</v>
+      </c>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1185,15 +1185,15 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cotton Leggings for Women Who Love Soft, Breathable Comfort</t>
+          <t>Black Leggings for Women: The Versatile Wardrobe Staple</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>cotton leggings for women</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
+          <t>black leggings for women</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -1212,11 +1212,11 @@
         <v>4400</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>30</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1231,22 +1231,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Compression Leggings for Women Who Push Their Workouts</t>
+          <t>Women's Tracksuit Pants: How to Choose Your Fit</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>compression leggings for women</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+          <t>tracksuit pants for ladies</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1277,15 +1277,15 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Black Leggings for Women: The Versatile Wardrobe Staple</t>
+          <t>Workout Pants for Women: Fit That Moves With You</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>black leggings for women</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
+          <t>workout pants for women</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -1297,18 +1297,18 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4400</v>
+        <v>2900</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>25</v>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1323,22 +1323,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Women's Tracksuit Pants: How to Choose Your Fit</t>
+          <t>Best Butt-Lifting Leggings for a Sculpted, Confident Shape</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>tracksuit pants for ladies</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
+          <t>best butt lifting leggings</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>3600</v>
+        <v>2400</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tummy-Control Leggings for Smooth, All-Day Support</t>
+          <t>Workout Sets: The Girlie Vault Guide to Matched Activewear</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>tummy control leggings</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>Leggings &amp; Bottoms</t>
+          <t>workout sets</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1393,14 +1393,14 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2900</v>
+        <v>40500</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>40</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1415,34 +1415,34 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Workout Sets: The Girlie Vault Guide to Matched Activewear</t>
+          <t>What to Know Before Buying a Two-Piece Set</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>workout sets</t>
-        </is>
-      </c>
-      <c r="E19" s="10" t="inlineStr">
+          <t>two piece sets</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>40500</v>
+        <v>27100</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1461,15 +1461,15 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Yoga Clothes: How to Build a Comfortable Practice Wardrobe</t>
+          <t>White Two-Piece Sets: Styling a Fresh Coordinated Look</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>yoga clothes</t>
-        </is>
-      </c>
-      <c r="E20" s="10" t="inlineStr">
+          <t>white two piece set</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
@@ -1485,14 +1485,14 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>9900</v>
+        <v>8100</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>22</v>
+      </c>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
           <t>plus size workout clothes</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
@@ -1536,7 +1536,7 @@
       <c r="I21" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="J21" s="9" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -1561,7 +1561,7 @@
           <t>sets for women</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
@@ -1599,38 +1599,38 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Yoga Clothes for Women Who Value Comfort and Stretch</t>
+          <t>Women's Gym Dresses: How to Find Your Perfect Fit</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>yoga clothes for women</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
+          <t>gym dress for ladies</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
         <v>4400</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>47</v>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>What to Wear to Pilates: Building a Comfortable Outfit</t>
+          <t>Building a Workout Routine You Can Stick To</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>what to wear to pilates</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
+          <t>workout routine for women</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1669,14 +1669,14 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>46</v>
+      </c>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -1691,36 +1691,36 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Racerback Bras: How to Choose the Right Support</t>
+          <t>How to Style Yoga Flare Pants for Any Occasion</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>racerback bra</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>yoga flare pants outfits</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>8100</v>
+        <v>2400</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+        <v>24</v>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1745,7 +1745,7 @@
           <t>cropped tank top</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -1766,7 +1766,7 @@
       <c r="I26" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J26" s="11" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -1783,15 +1783,15 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Racerback Tanks: Finding Your Best Fit and Feel</t>
+          <t>High-Support Sports Bras: Lock-In Coverage for Any Impact</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>racerback tank</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
+          <t>high sports bra support</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -1803,18 +1803,18 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
         <v>4400</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>37</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
           <t>plus size sports bra</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -1858,7 +1858,7 @@
       <c r="I28" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1875,15 +1875,15 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Push-Up Sports Bras: How to Find Support and Shape</t>
+          <t>Yellow Tank Tops: Styling a Bright, Bold Basic</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>push up sports bra</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
+          <t>yellow tank top</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -1902,9 +1902,9 @@
         <v>3600</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -1921,38 +1921,38 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Cute Hooded Sweatshirts for Women to Layer and Lounge</t>
+          <t>Cotton Sports Bras: Soft Support for Low-Impact Days</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>cute hooded sweatshirts for women</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
+          <t>cotton sports bra</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>18</v>
+      </c>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1967,38 +1967,38 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>One-Piece Swimsuits: How to Find Your Perfect Fit</t>
+          <t>The Best Seamless Sports Bras for Everyday Comfort</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>one piece swimsuit</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Swimwear &amp; Beach</t>
+          <t>seamless sports bra</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49500</v>
+        <v>1300</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>9</v>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>One-Piece Swimsuits: Your Complete Buying Guide</t>
+          <t>Tankini Swimsuits: How to Find Your Perfect Fit</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>one piece swimwear swimsuits</t>
+          <t>tankini swimsuit</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -2033,18 +2033,18 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>33100</v>
+        <v>22200</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>28</v>
+      </c>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>What to Know Before Buying a Two-Piece Set</t>
+          <t>What to Know Before You Buy a String Bikini</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>two piece sets</t>
+          <t>string bikini</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -2083,14 +2083,14 @@
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>27100</v>
+        <v>22200</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>24</v>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       <c r="I34" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Women's Swim Shorts: A Buyer's Guide to Coverage and Comfort</t>
+          <t>The Best Tummy-Control Swimsuits for Every Body</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>bathing shorts for ladies</t>
+          <t>tummy control swimsuit</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -2166,21 +2166,21 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
         <v>14800</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="J35" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2226,7 +2226,7 @@
       <c r="I36" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>What Makes a Two-Piece Swimsuit Actually Fit Right</t>
+          <t>Swim Skirts: Flattering Coverage for Beach and Pool</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>two piece swimsuit</t>
+          <t>swim skirt</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -2258,21 +2258,21 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
         <v>8100</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2289,12 +2289,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>One-Piece Swimsuits for Women of Every Shape</t>
+          <t>Black One-Piece Swimsuits: The Everyday Flattering Staple</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>one piece swimsuits for women</t>
+          <t>black one piece swimsuit</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2316,11 +2316,11 @@
         <v>8100</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>26</v>
+      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>High-Waisted vs Mid-Rise Bikini Bottoms: Which Flatters You</t>
+          <t>Bikini Bottoms: How to Find Your Most Flattering Cut</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>high waisted bikini bottoms</t>
+          <t>bikini bottoms</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2362,9 +2362,9 @@
         <v>6600</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>How Tummy-Control Swimsuits Smooth and Support You</t>
+          <t>High-Waisted vs Mid-Rise Bikini Bottoms: Which Flatters You</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>tummy control bathers</t>
+          <t>high waisted bikini bottoms</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -2401,16 +2401,16 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>5400</v>
+        <v>6600</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Swim Shirts for Women: Sun-Smart Coverage With Style</t>
+          <t>Two-Piece Swimsuits: A Buyer's Guide for Women</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>swim shirts for women</t>
+          <t>two piece swimming costumes for ladies</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -2442,21 +2442,21 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="J41" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2473,12 +2473,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Your Essential Women's Sportswear Checklist</t>
+          <t>The Best Sports Bras for Women: A Support Guide</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>sportswear list</t>
+          <t>sports bras for women</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2488,23 +2488,23 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
         <v>8100</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>50</v>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Moisture-Wicking Shirts: How to Choose Your Workout Top</t>
+          <t>Sports Bags: How to Pick the Right Gym Bag</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>moisture wicking shirts</t>
+          <t>sports bag</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2539,14 +2539,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
       <c r="I44" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -2640,7 +2640,7 @@
       <c r="I45" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Cotton Sports Bras: Soft Support for Low-Impact Days</t>
+          <t>What Moisture-Wicking Fabric Does for Your Workout</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>cotton sports bra</t>
+          <t>moisture wicking</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2672,23 +2672,23 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>44</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2703,15 +2703,15 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Girlie Vault Reviews: What Women Say About Fit and Feel</t>
+          <t>Becoming a Girlie Vault Ambassador: Inside Our Community</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>girlie vault reviews</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+          <t>girlie vault ambassador</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -2736,7 +2736,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -2761,7 +2761,7 @@
           <t>give back girls</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -2786,7 +2786,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
+      <c r="J48" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -2811,7 +2811,7 @@
           <t>activewear brand that gives back</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -2836,7 +2836,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J49" s="7" t="inlineStr">
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -2861,7 +2861,7 @@
           <t>purpose driven fashion brand</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -2886,7 +2886,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -2903,34 +2903,34 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Capri Pants: A Buyer's Guide to Fit and Length</t>
+          <t>What Makes a Great Pair of Yoga Pants</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>capri pants</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
+          <t>yoga pants</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>33100</v>
+        <v>40500</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
@@ -2949,15 +2949,15 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>The Girlie Vault Guide to Flare Leggings</t>
+          <t>Capri Pants: A Buyer's Guide to Fit and Length</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>flare leggings</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
+          <t>capri pants</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -2973,10 +2973,10 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>27100</v>
+        <v>33100</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -2995,22 +2995,22 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Joggers for Women: Comfort That Goes Anywhere</t>
+          <t>The Girlie Vault Guide to Flare Leggings</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>joggers for women</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
+          <t>flare leggings</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>14800</v>
+        <v>27100</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3041,15 +3041,15 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Straight-Leg Sweatpants: A Buyer's Guide to Fit and Fabric</t>
+          <t>Athletic Shorts: Choosing the Right Pair for Every Workout</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>straight leg sweatpants</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr">
+          <t>athletic shorts</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -3061,18 +3061,18 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>12100</v>
+        <v>22200</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>48</v>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -3087,15 +3087,15 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Cotton Leggings: A Buyer's Guide to Softness and Support</t>
+          <t>Straight-Leg Sweatpants: A Buyer's Guide to Fit and Fabric</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>cotton leggings</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
+          <t>straight leg sweatpants</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -3111,12 +3111,12 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>8100</v>
+        <v>12100</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J55" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3133,38 +3133,38 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Women's Capri Leggings: A Buyer's Guide to Fit</t>
+          <t>The Best Compression Leggings for Squat-Proof Coverage</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>capri trousers for ladies</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
+          <t>compression leggings</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>8100</v>
+        <v>12100</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>24</v>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -3179,22 +3179,22 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>High-Waisted Leggings for All-Day Comfort and Support</t>
+          <t>Workout Shorts: Finding the Right Length and Fit</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>high waisted leggings</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
+          <t>workout shorts</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -3203,10 +3203,10 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>6600</v>
+        <v>9900</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
@@ -3225,34 +3225,34 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Capris for Women: Cropped Comfort Done Right</t>
+          <t>Leggings With Pockets: How to Find the Most Functional Pair</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>capris for women</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
+          <t>leggings with pockets</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>5400</v>
+        <v>9900</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
@@ -3271,38 +3271,38 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Seamless Leggings for a Smooth, Sculpted Fit</t>
+          <t>Yoga Shorts: How to Pick Your Perfect Pair</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>seamless leggings</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
+          <t>yoga shorts</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>4400</v>
+        <v>6600</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>22</v>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -3317,34 +3317,34 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Two-Piece Sets: How to Choose a Coordinated Look</t>
+          <t>High-Waisted Leggings for All-Day Comfort and Support</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>2 piece sets</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>high waisted leggings</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>14800</v>
+        <v>6600</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
@@ -3363,17 +3363,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Two-Piece Sets for Women: A Buyer's Guide</t>
+          <t>Fold-Over Leggings: Choosing Your Comfiest Waistband</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>two piece sets women</t>
-        </is>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>fold over leggings</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -3387,14 +3387,14 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>12100</v>
+        <v>5400</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>19</v>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -3409,22 +3409,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Workout Sets for Women: Coordinated and Comfortable</t>
+          <t>Women's Board Shorts: Active Coverage for Sun and Surf</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>workout sets for women</t>
-        </is>
-      </c>
-      <c r="E62" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>womens board shorts</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>8100</v>
+        <v>5400</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>23</v>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -3455,22 +3455,22 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>How to Put Together Pilates Outfits You Feel Good In</t>
+          <t>Tummy-Control Leggings for Smooth, All-Day Support</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>pilates outfits</t>
-        </is>
-      </c>
-      <c r="E63" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>tummy control leggings</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>6600</v>
+        <v>2900</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3501,15 +3501,15 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Women's Gym Dresses: How to Find Your Perfect Fit</t>
+          <t>Matching Sets for Women: Finding Your Perfect Pairing</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>gym dress for ladies</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
+          <t>matching sets women</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
@@ -3521,18 +3521,18 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>4400</v>
+        <v>14800</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="J64" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>38</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -3547,15 +3547,15 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>How to Style Matching Outfits That Actually Work</t>
+          <t>How to Put Together Pilates Outfits You Feel Good In</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>matching outfits</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
+          <t>pilates outfits</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
@@ -3567,16 +3567,16 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>4400</v>
+        <v>6600</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3593,22 +3593,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>How to Style Yoga Flare Pants for Any Occasion</t>
+          <t>Summer Sets: Easy Coordinated Warm-Weather Outfits</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>yoga flare pants outfits</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
+          <t>summer sets</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>2400</v>
+        <v>5400</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3639,38 +3639,38 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>How to Build a Workout Plan Women Can Stick To</t>
+          <t>Yoga Clothes for Women Who Value Comfort and Stretch</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>workout plan for ladies</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
+          <t>yoga clothes for women</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2400</v>
+        <v>4400</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>32</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -3685,22 +3685,22 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Tank Tops With Built-In Bras: Finding Your Perfect Fit</t>
+          <t>Women's Gym Sets: Pieces That Work as Hard as You</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>tank top with built in bra</t>
-        </is>
-      </c>
-      <c r="E68" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>gym sets for women</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3709,14 +3709,14 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>6600</v>
+        <v>2900</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>30</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -3731,38 +3731,38 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>How to Find the Best Sports Bra for Your Workout</t>
+          <t>How to Build a Workout Plan Women Can Stick To</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>best sports bra</t>
-        </is>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>workout plan for ladies</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>5400</v>
+        <v>2400</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>26</v>
+      </c>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -3777,15 +3777,15 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Choosing a Great Sports Bra for a Larger Chest</t>
+          <t>Racerback Bras: How to Choose the Right Support</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>good sports bra for large chest</t>
-        </is>
-      </c>
-      <c r="E70" s="12" t="inlineStr">
+          <t>racerback bra</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -3797,16 +3797,16 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>4400</v>
+        <v>8100</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="J70" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3823,15 +3823,15 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>White Sports Bras: How to Pick the Perfect One</t>
+          <t>Tank Tops With Built-In Bras: Finding Your Perfect Fit</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>white sports bra</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
+          <t>tank top with built in bra</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -3843,16 +3843,16 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>3600</v>
+        <v>6600</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="J71" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3869,22 +3869,22 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>The Best Compression Sports Bras for High-Impact Support</t>
+          <t>Racerback Tanks: Finding Your Best Fit and Feel</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>compression sports bra</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
+          <t>racerback tank</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>2900</v>
+        <v>4400</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3915,36 +3915,36 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Cropped Pants for Women: Style Meets Movement</t>
+          <t>Push-Up Sports Bras: How to Find Support and Shape</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>cropped pants for women</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
+          <t>push up sports bra</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>1900</v>
+        <v>3600</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -3961,15 +3961,15 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>The Best Seamless Sports Bras for Everyday Comfort</t>
+          <t>The Best Compression Sports Bras for High-Impact Support</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>seamless sports bra</t>
-        </is>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
+          <t>compression sports bra</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -3985,14 +3985,14 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>1300</v>
+        <v>2900</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>15</v>
+      </c>
+      <c r="J74" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -4007,34 +4007,34 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Matching Sets: A Buyer's Guide to Effortless Outfits</t>
+          <t>Cute Hooded Sweatshirts for Women to Layer and Lounge</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>matching sets</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="inlineStr">
-        <is>
-          <t>Swimwear &amp; Beach</t>
+          <t>cute hooded sweatshirts for women</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>27100</v>
+        <v>2400</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
@@ -4053,36 +4053,36 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Tankini Swimsuits: How to Find Your Perfect Fit</t>
+          <t>Cropped Pants for Women: Style Meets Movement</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>tankini swimsuit</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>Swimwear &amp; Beach</t>
+          <t>cropped pants for women</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>22200</v>
+        <v>1900</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4099,36 +4099,36 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>What to Know Before You Buy a String Bikini</t>
+          <t>Best Sports Bras for Running: What to Look For</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>string bikini</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>Swimwear &amp; Beach</t>
+          <t>best sports bra for running</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>22200</v>
+        <v>1900</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="J77" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>The Best Tummy-Control Swimsuits for Every Body</t>
+          <t>Tankini Beachwear: Coverage and Confidence in One</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>tummy control swimsuit</t>
+          <t>tankini beachwear</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>14800</v>
+        <v>6600</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>High-Waisted Swimsuits for Flattering, Confident Coverage</t>
+          <t>How to Choose Women's Swim Trunks for Comfort</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>high waisted swimsuit</t>
+          <t>swimming trunk for ladies</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
@@ -4206,21 +4206,21 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>5400</v>
+        <v>6600</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="J79" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Best Bathing Suits for Women: What to Look For</t>
+          <t>High-Waisted Beachwear That Flatters and Stays Put</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>best bathing suits for women</t>
+          <t>high waisted beachwear</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
@@ -4261,14 +4261,14 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>17</v>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -4283,12 +4283,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>High-Waisted Beachwear That Flatters and Stays Put</t>
+          <t>One-Piece Swimsuits With Built-In Tummy Control</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>high waisted beachwear</t>
+          <t>1 piece swimsuit tummy control</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
@@ -4303,18 +4303,18 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>13</v>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Women's Sweatpants: Choosing Your Everyday Pair</t>
+          <t>Athletic Dresses: How to Find Your Perfect Fit</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>sweatpants women</t>
+          <t>athletic dress</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>18100</v>
+        <v>12100</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Athletic Dresses: How to Find Your Perfect Fit</t>
+          <t>Workout Pants: The Girlie Vault Guide to Fitness Bottoms</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>athletic dress</t>
+          <t>pants for fitness</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -4399,14 +4399,14 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>12100</v>
+        <v>4400</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>19</v>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>The Best Sports Bras for Women: A Support Guide</t>
+          <t>Women's Track Pants: Sporty Comfort On and Off the Track</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>sports bras for women</t>
+          <t>track pants women</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -4436,23 +4436,23 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>8100</v>
+        <v>4400</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>28</v>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Sweatpants for Women: Where Cozy Meets Vibrant</t>
+          <t>What to Look For in a Sportswear Brand You Can Trust</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>sweat pants for women</t>
+          <t>sportswear brands</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -4482,23 +4482,23 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>5400</v>
+        <v>4400</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>50</v>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Workout Pants: The Girlie Vault Guide to Fitness Bottoms</t>
+          <t>Yoga Tops: Breathable Styles That Move With You</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>pants for fitness</t>
+          <t>yoga tops</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -4533,16 +4533,16 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Workout Shirts for Women: Breathable, Bright, and Built to Move</t>
+          <t>Jogging Suits for Women: Matched and Movement-Ready</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>workout shirts for women</t>
+          <t>jogging suits for women</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -4579,14 +4579,14 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
         <v>3600</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Best Sports Bras for Big Busts: What to Look For</t>
+          <t>Gym Trousers: Comfortable Bottoms for Every Workout</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>best sports bras for big boobs</t>
+          <t>trouser for gym</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -4620,23 +4620,23 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>39</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4651,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Running Clothes for Women in Every Season</t>
+          <t>The Best High-Impact Sports Bras for Serious Support</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>running clothes for women</t>
+          <t>high impact sports bras</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -4671,18 +4671,18 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>26</v>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -4697,38 +4697,42 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>The Best High-Impact Sports Bras for Serious Support</t>
+          <t>What Take the Pledge Means: How Your Purchase Helps Feed Families</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>high impact sports bras</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>Activewear Style &amp; Education</t>
+          <t>take the pledge meaning</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Brand, Give-Back &amp; Community</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Branded</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Brand</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4747,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Becoming a Girlie Vault Ambassador: Inside Our Community</t>
+          <t>Why We Build Activewear to Help Women Stand Out</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>girlie vault ambassador</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
+          <t>women empowerment activewear</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -4776,7 +4780,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J91" s="7" t="inlineStr">
+      <c r="J91" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -4793,15 +4797,15 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Why We Build Activewear to Help Women Stand Out</t>
+          <t>How the Take the Pledge Collection Supports City Harvest</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>women empowerment activewear</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
+          <t>city harvest pledge collection</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
@@ -4826,7 +4830,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
+      <c r="J92" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -4843,22 +4847,22 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>How the Take the Pledge Collection Supports City Harvest</t>
+          <t>Our Mission: Comfortable, Vibrant Activewear With Heart</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>city harvest pledge collection</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
+          <t>women owned activewear mission</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>Brand, Give-Back &amp; Community</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -4876,7 +4880,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J93" s="7" t="inlineStr">
+      <c r="J93" s="6" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
@@ -4893,42 +4897,38 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Our Mission: Comfortable, Vibrant Activewear With Heart</t>
+          <t>Sweatpants: A Buyer's Guide to Comfort and Fit</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>women owned activewear mission</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>Brand, Give-Back &amp; Community</t>
+          <t>sweat pants</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Branded</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr">
-        <is>
-          <t>Brand</t>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>40500</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -4943,34 +4943,34 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>What Makes a Great Pair of Yoga Pants</t>
+          <t>Running Shorts: A Buyer's Guide to Fit and Freedom</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>yoga pants</t>
-        </is>
-      </c>
-      <c r="E95" s="8" t="inlineStr">
+          <t>running shorts</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40500</v>
+        <v>27100</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -4989,34 +4989,34 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Running Shorts: A Buyer's Guide to Fit and Freedom</t>
+          <t>Joggers for Women: Comfort That Goes Anywhere</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>running shorts</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
+          <t>joggers for women</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>27100</v>
+        <v>14800</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
@@ -5035,38 +5035,38 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Athletic Shorts: Choosing the Right Pair for Every Workout</t>
+          <t>The Best Scrunch-Butt Leggings for Squat-Proof Shape</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>athletic shorts</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
+          <t>scrunch butt leggings</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>22200</v>
+        <v>6600</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>18</v>
+      </c>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5081,15 +5081,15 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>The Best Compression Leggings for Squat-Proof Coverage</t>
+          <t>Best Leggings for Women: What to Look For</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>compression leggings</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
+          <t>best leggings for women</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -5105,14 +5105,14 @@
         </is>
       </c>
       <c r="H98" s="2" t="n">
-        <v>12100</v>
+        <v>6600</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>46</v>
+      </c>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -5127,15 +5127,15 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Workout Shorts: Finding the Right Length and Fit</t>
+          <t>Women's Wide-Leg Sweatpants: Relaxed Comfort, Elevated</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>workout shorts</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
+          <t>wide leg sweatpants women</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -5151,14 +5151,14 @@
         </is>
       </c>
       <c r="H99" s="2" t="n">
-        <v>9900</v>
+        <v>5400</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>27</v>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5173,34 +5173,34 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Leggings With Pockets: How to Find the Most Functional Pair</t>
+          <t>Capris for Women: Cropped Comfort Done Right</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>leggings with pockets</t>
-        </is>
-      </c>
-      <c r="E100" s="8" t="inlineStr">
+          <t>capris for women</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H100" s="2" t="n">
-        <v>9900</v>
+        <v>5400</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
@@ -5219,36 +5219,36 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Capri Leggings: A Buyer's Guide to Fit and Length</t>
+          <t>Plus-Size Leggings That Fit, Flatter, and Move With You</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>capri leggings</t>
-        </is>
-      </c>
-      <c r="E101" s="8" t="inlineStr">
+          <t>plus size leggings</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>8100</v>
+        <v>4400</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
+        <v>26</v>
+      </c>
+      <c r="J101" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5265,15 +5265,15 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Capri Pants for Women: Versatile Fit for Any Activity</t>
+          <t>Long Shorts for Women: More Coverage, Same Style</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>capri pants for women</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
+          <t>long shorts for women</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -5285,18 +5285,18 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>8100</v>
+        <v>4400</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>27</v>
+      </c>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5311,15 +5311,15 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>The Best Scrunch-Butt Leggings for Squat-Proof Shape</t>
+          <t>Seamless Leggings for a Smooth, Sculpted Fit</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>scrunch butt leggings</t>
-        </is>
-      </c>
-      <c r="E103" s="8" t="inlineStr">
+          <t>seamless leggings</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>Leggings &amp; Bottoms</t>
         </is>
@@ -5335,14 +5335,14 @@
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>31</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Best Leggings for Women: What to Look For</t>
+          <t>Loungewear Sets: Cozy, Coordinated, Ready to Relax</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>best leggings for women</t>
-        </is>
-      </c>
-      <c r="E104" s="8" t="inlineStr">
-        <is>
-          <t>Leggings &amp; Bottoms</t>
+          <t>loungewear sets</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -5381,14 +5381,14 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>6600</v>
+        <v>8100</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="J104" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>38</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -5403,17 +5403,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Long Shorts for Women: More Coverage, Same Style</t>
+          <t>Lounge Sets for Women: Cozy, Vibrant, Easy to Love</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>long shorts for women</t>
-        </is>
-      </c>
-      <c r="E105" s="8" t="inlineStr">
-        <is>
-          <t>Leggings &amp; Bottoms</t>
+          <t>lounge sets for women</t>
+        </is>
+      </c>
+      <c r="E105" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -5423,18 +5423,18 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H105" s="2" t="n">
-        <v>4400</v>
+        <v>6600</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>39</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -5449,36 +5449,36 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Workout Pants for Women: Fit That Moves With You</t>
+          <t>How to Style Matching Outfits That Actually Work</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>workout pants for women</t>
-        </is>
-      </c>
-      <c r="E106" s="8" t="inlineStr">
-        <is>
-          <t>Leggings &amp; Bottoms</t>
+          <t>matching outfits</t>
+        </is>
+      </c>
+      <c r="E106" s="9" t="inlineStr">
+        <is>
+          <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H106" s="2" t="n">
-        <v>2900</v>
+        <v>4400</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="J106" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5495,38 +5495,38 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Matching Sets for Women: Finding Your Perfect Pairing</t>
+          <t>What to Wear to Pilates: Building a Comfortable Outfit</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>matching sets women</t>
-        </is>
-      </c>
-      <c r="E107" s="10" t="inlineStr">
+          <t>what to wear to pilates</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="inlineStr">
         <is>
           <t>Matching Sets &amp; Outfits</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="H107" s="2" t="n">
-        <v>14800</v>
+        <v>2400</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>8</v>
+      </c>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -5541,17 +5541,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Lounge Sets: How to Find Your Coziest Match</t>
+          <t>Pink Tank Tops: Styling a Vibrant Wardrobe Staple</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>lounge set</t>
-        </is>
-      </c>
-      <c r="E108" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>pink tank top</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -5565,14 +5565,14 @@
         </is>
       </c>
       <c r="H108" s="2" t="n">
-        <v>9900</v>
+        <v>4400</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>26</v>
+      </c>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5587,38 +5587,38 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Lounge Sets for Women: Cozy, Vibrant, Easy to Love</t>
+          <t>White Sports Bras: How to Pick the Perfect One</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>lounge sets for women</t>
-        </is>
-      </c>
-      <c r="E109" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>white sports bra</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H109" s="2" t="n">
-        <v>6600</v>
+        <v>3600</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>18</v>
+      </c>
+      <c r="J109" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5633,22 +5633,22 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Two-Piece Clothing Sets for Women Who Love to Coordinate</t>
+          <t>Workout Tank Tops: How to Choose Your Go-To</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>two piece clothing sets for women</t>
-        </is>
-      </c>
-      <c r="E110" s="10" t="inlineStr">
-        <is>
-          <t>Matching Sets &amp; Outfits</t>
+          <t>workout tank tops</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
         </is>
       </c>
       <c r="H110" s="2" t="n">
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="J110" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5679,22 +5679,22 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Pink Tank Tops: Styling a Vibrant Wardrobe Staple</t>
+          <t>Best Sports Bras for Large Breasts: What to Look For</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>pink tank top</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="inlineStr">
+          <t>best sports bra for large breasts</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
         </is>
       </c>
       <c r="H111" s="2" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
+        <v>16</v>
+      </c>
+      <c r="J111" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5725,15 +5725,15 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Yellow Tank Tops: Styling a Bright, Bold Basic</t>
+          <t>Athletic Jackets: How to Layer for Every Workout</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>yellow tank top</t>
-        </is>
-      </c>
-      <c r="E112" s="12" t="inlineStr">
+          <t>athletic jacket</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
@@ -5749,12 +5749,12 @@
         </is>
       </c>
       <c r="H112" s="2" t="n">
-        <v>3600</v>
+        <v>2900</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J112" s="5" t="inlineStr">
+        <v>27</v>
+      </c>
+      <c r="J112" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5771,22 +5771,22 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Workout Tank Tops: How to Choose Your Go-To</t>
+          <t>Workout Tanks for Women: Breathable, Bold, Ready to Move</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>workout tank tops</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
+          <t>workout tanks for women</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
         <is>
           <t>Sports Bras &amp; Tops</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
         </is>
       </c>
       <c r="H113" s="2" t="n">
-        <v>3600</v>
+        <v>1600</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J113" s="5" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="J113" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5817,38 +5817,38 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Best Sports Bras for Large Breasts: What to Look For</t>
+          <t>One-Piece Swimsuits: How to Find Your Perfect Fit</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>best sports bra for large breasts</t>
-        </is>
-      </c>
-      <c r="E114" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>one piece swimsuit</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="inlineStr">
+        <is>
+          <t>Swimwear &amp; Beach</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="H114" s="2" t="n">
-        <v>3600</v>
+        <v>49500</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J114" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>35</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -5863,22 +5863,22 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Best Sports Bras for Bigger Breasts: What to Look For</t>
+          <t>Swimsuit Cover-Up Dresses: How to Find Your Fit</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>best sports bra for bigger breasts</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>dresses for bathing suits</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>Swimwear &amp; Beach</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -5887,14 +5887,14 @@
         </is>
       </c>
       <c r="H115" s="2" t="n">
-        <v>1900</v>
+        <v>9900</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J115" s="11" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>23</v>
+      </c>
+      <c r="J115" s="8" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -5909,22 +5909,22 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Best Sports Bras for Running: What to Look For</t>
+          <t>Triangle Bikini Tops: How to Find Your Best Fit</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>best sports bra for running</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>triangle bikini top</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>Swimwear &amp; Beach</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
         </is>
       </c>
       <c r="H116" s="2" t="n">
-        <v>1900</v>
+        <v>6600</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="J116" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J116" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -5955,17 +5955,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Workout Tanks for Women: Breathable, Bold, Ready to Move</t>
+          <t>Best Swimsuits for Women: What to Look For</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>workout tanks for women</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Sports Bras &amp; Tops</t>
+          <t>best swimsuits for ladies</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>Swimwear &amp; Beach</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -5979,14 +5979,14 @@
         </is>
       </c>
       <c r="H117" s="2" t="n">
-        <v>1600</v>
+        <v>6600</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>45</v>
+      </c>
+      <c r="J117" s="10" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
     </row>
@@ -6001,12 +6001,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Swimsuit Cover-Up Dresses: How to Find Your Fit</t>
+          <t>High-Waisted Swimsuits for Flattering, Confident Coverage</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>dresses for bathing suits</t>
+          <t>high waisted swimsuit</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
         </is>
       </c>
       <c r="H118" s="2" t="n">
-        <v>9900</v>
+        <v>5400</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J118" s="5" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6047,12 +6047,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>How to Choose Women's Swim Trunks for Comfort</t>
+          <t>Swim Shirts for Women: Sun-Smart Coverage With Style</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>swimming trunk for ladies</t>
+          <t>swim shirts for women</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
@@ -6062,21 +6062,21 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H119" s="2" t="n">
-        <v>6600</v>
+        <v>4400</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
+        <v>24</v>
+      </c>
+      <c r="J119" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Best Swimsuits for Women: What to Look For</t>
+          <t>Tummy-Control Bikinis: Smoothing Support, Bikini Style</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>best swimsuits for ladies</t>
+          <t>tummy control bikini</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
@@ -6117,14 +6117,14 @@
         </is>
       </c>
       <c r="H120" s="2" t="n">
-        <v>6600</v>
+        <v>2900</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>14</v>
+      </c>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
     </row>
@@ -6139,12 +6139,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Two-Piece Swimsuits: A Buyer's Guide for Women</t>
+          <t>Women's Swim Tops: Coverage, Support, and Style</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>two piece swimming costumes for ladies</t>
+          <t>swim tops for women</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
@@ -6154,21 +6154,21 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="H121" s="2" t="n">
-        <v>5400</v>
+        <v>2400</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
+        <v>23</v>
+      </c>
+      <c r="J121" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6250,7 +6250,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6278,7 +6278,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6306,7 +6306,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6324,7 +6324,7 @@
       <c r="C5" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -6334,7 +6334,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6362,7 +6362,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6390,9 +6390,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6446,7 +6446,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6474,7 +6474,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6502,9 +6502,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       <c r="C15" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -6632,7 +6632,7 @@
       <c r="C16" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6642,7 +6642,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6660,7 +6660,7 @@
       <c r="C17" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6670,7 +6670,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6688,7 +6688,7 @@
       <c r="C18" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -6698,7 +6698,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6716,7 +6716,7 @@
       <c r="C19" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -6744,7 +6744,7 @@
       <c r="C20" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6754,7 +6754,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6772,7 +6772,7 @@
       <c r="C21" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6810,7 +6810,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6838,7 +6838,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6866,7 +6866,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -6884,7 +6884,7 @@
       <c r="C25" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6894,9 +6894,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       <c r="C26" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6968,7 +6968,7 @@
       <c r="C28" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -6978,7 +6978,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7006,9 +7006,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7062,7 +7062,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7080,7 +7080,7 @@
       <c r="C32" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -7108,7 +7108,7 @@
       <c r="C33" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7118,7 +7118,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7136,7 +7136,7 @@
       <c r="C34" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7146,7 +7146,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7164,7 +7164,7 @@
       <c r="C35" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7192,7 +7192,7 @@
       <c r="C36" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7202,7 +7202,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7230,9 +7230,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       <c r="C38" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -7276,7 +7276,7 @@
       <c r="C39" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7286,7 +7286,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7314,7 +7314,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7332,7 +7332,7 @@
       <c r="C41" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7370,7 +7370,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7388,7 +7388,7 @@
       <c r="C43" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7416,7 +7416,7 @@
       <c r="C44" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7444,7 +7444,7 @@
       <c r="C45" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7472,7 +7472,7 @@
       <c r="C46" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -7510,9 +7510,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       <c r="C49" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -7594,9 +7594,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       <c r="C51" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7622,9 +7622,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7640,7 +7640,7 @@
       <c r="C52" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7650,9 +7650,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       <c r="C53" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7678,9 +7678,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       <c r="C54" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -7752,7 +7752,7 @@
       <c r="C56" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7780,7 +7780,7 @@
       <c r="C57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7790,7 +7790,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F57" s="8" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7808,7 +7808,7 @@
       <c r="C58" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D58" s="5" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7836,7 +7836,7 @@
       <c r="C59" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7846,9 +7846,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       <c r="C60" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -7874,7 +7874,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -7920,7 +7920,7 @@
       <c r="C62" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D62" s="5" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7948,7 +7948,7 @@
       <c r="C63" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D63" s="5" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7958,9 +7958,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       <c r="C64" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D64" s="5" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -7986,9 +7986,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8042,9 +8042,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
       <c r="C67" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8088,7 +8088,7 @@
       <c r="C68" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D68" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8098,9 +8098,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8154,9 +8154,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8182,9 +8182,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       <c r="C72" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D72" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8228,7 +8228,7 @@
       <c r="C73" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D73" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8266,9 +8266,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8322,9 +8322,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8340,7 @@
       <c r="C77" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8350,9 +8350,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8406,9 +8406,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       <c r="C81" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D81" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8480,7 +8480,7 @@
       <c r="C82" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8508,7 +8508,7 @@
       <c r="C83" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D83" s="9" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8536,7 +8536,7 @@
       <c r="C84" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8546,7 +8546,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8564,7 +8564,7 @@
       <c r="C85" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D85" s="5" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8574,9 +8574,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       <c r="C86" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8620,7 +8620,7 @@
       <c r="C87" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D87" s="5" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8648,7 +8648,7 @@
       <c r="C88" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D88" s="5" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8658,9 +8658,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       <c r="C89" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D89" s="5" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8686,7 +8686,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8714,7 +8714,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8742,7 +8742,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8788,7 +8788,7 @@
       <c r="C93" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8798,7 +8798,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8816,7 +8816,7 @@
       <c r="C94" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D94" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8826,7 +8826,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8844,7 +8844,7 @@
       <c r="C95" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D95" s="5" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8872,7 +8872,7 @@
       <c r="C96" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D96" s="5" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8882,7 +8882,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F96" s="8" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8928,7 +8928,7 @@
       <c r="C98" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D98" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -8956,7 +8956,7 @@
       <c r="C99" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8966,7 +8966,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F99" s="8" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -8984,7 +8984,7 @@
       <c r="C100" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -8994,9 +8994,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       <c r="C101" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9022,7 +9022,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F101" s="8" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9040,7 +9040,7 @@
       <c r="C102" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9050,9 +9050,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       <c r="C103" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D103" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9096,7 +9096,7 @@
       <c r="C104" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D104" s="5" t="inlineStr">
+      <c r="D104" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9152,7 +9152,7 @@
       <c r="C106" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D106" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9208,7 +9208,7 @@
       <c r="C108" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D108" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9218,7 +9218,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9236,7 +9236,7 @@
       <c r="C109" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D109" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9292,7 +9292,7 @@
       <c r="C111" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D111" s="5" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9302,9 +9302,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       <c r="C112" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D112" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9348,7 +9348,7 @@
       <c r="C113" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D113" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9432,7 +9432,7 @@
       <c r="C116" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -9498,7 +9498,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9516,7 +9516,7 @@
       <c r="C119" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D119" s="9" t="inlineStr">
+      <c r="D119" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9554,9 +9554,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F120" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9572,7 @@
       <c r="C121" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D121" s="9" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9600,7 +9600,7 @@
       <c r="C122" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D122" s="9" t="inlineStr">
+      <c r="D122" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -9628,7 +9628,7 @@
       <c r="C123" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D123" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -9656,7 +9656,7 @@
       <c r="C124" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -9684,7 +9684,7 @@
       <c r="C125" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D125" s="5" t="inlineStr">
+      <c r="D125" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9712,7 +9712,7 @@
       <c r="C126" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D126" s="5" t="inlineStr">
+      <c r="D126" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9740,7 +9740,7 @@
       <c r="C127" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D127" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9768,7 +9768,7 @@
       <c r="C128" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9778,9 +9778,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       <c r="C129" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D129" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9824,7 +9824,7 @@
       <c r="C130" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D130" s="5" t="inlineStr">
+      <c r="D130" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9834,7 +9834,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F130" s="8" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -9880,7 +9880,7 @@
       <c r="C132" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D132" s="5" t="inlineStr">
+      <c r="D132" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9908,7 +9908,7 @@
       <c r="C133" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -9992,7 +9992,7 @@
       <c r="C136" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D136" s="9" t="inlineStr">
+      <c r="D136" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10020,7 +10020,7 @@
       <c r="C137" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10030,9 +10030,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F137" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10076,7 +10076,7 @@
       <c r="C139" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10086,9 +10086,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       <c r="C140" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D140" s="5" t="inlineStr">
+      <c r="D140" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10188,7 +10188,7 @@
       <c r="C143" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D143" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10198,7 +10198,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10216,7 +10216,7 @@
       <c r="C144" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D144" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -10244,7 +10244,7 @@
       <c r="C145" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D145" s="5" t="inlineStr">
+      <c r="D145" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10272,7 +10272,7 @@
       <c r="C146" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D146" s="5" t="inlineStr">
+      <c r="D146" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10282,9 +10282,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10356,7 +10356,7 @@
       <c r="C149" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D149" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10394,7 +10394,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F150" s="8" t="inlineStr">
+      <c r="F150" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10412,7 +10412,7 @@
       <c r="C151" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10440,7 +10440,7 @@
       <c r="C152" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10468,7 +10468,7 @@
       <c r="C153" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="D153" s="9" t="inlineStr">
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10552,7 +10552,7 @@
       <c r="C156" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D156" s="5" t="inlineStr">
+      <c r="D156" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10580,7 +10580,7 @@
       <c r="C157" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D157" s="5" t="inlineStr">
+      <c r="D157" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10618,9 +10618,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F158" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10636,7 +10636,7 @@
       <c r="C159" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D159" s="5" t="inlineStr">
+      <c r="D159" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10646,9 +10646,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F159" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       <c r="C160" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D160" s="5" t="inlineStr">
+      <c r="D160" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10674,9 +10674,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F161" s="8" t="inlineStr">
+      <c r="F161" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10720,7 +10720,7 @@
       <c r="C162" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="D162" s="9" t="inlineStr">
+      <c r="D162" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -10786,9 +10786,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       <c r="C165" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D165" s="5" t="inlineStr">
+      <c r="D165" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10814,9 +10814,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F165" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       <c r="C168" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D168" s="5" t="inlineStr">
+      <c r="D168" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10898,7 +10898,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="F168" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10916,7 +10916,7 @@
       <c r="C169" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D169" s="11" t="inlineStr">
+      <c r="D169" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -10926,7 +10926,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F169" s="8" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -10944,7 +10944,7 @@
       <c r="C170" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D170" s="5" t="inlineStr">
+      <c r="D170" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -10972,7 +10972,7 @@
       <c r="C171" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D171" s="5" t="inlineStr">
+      <c r="D171" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11000,7 +11000,7 @@
       <c r="C172" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D172" s="5" t="inlineStr">
+      <c r="D172" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11028,7 +11028,7 @@
       <c r="C173" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D173" s="11" t="inlineStr">
+      <c r="D173" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -11056,7 +11056,7 @@
       <c r="C174" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D174" s="9" t="inlineStr">
+      <c r="D174" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -11140,7 +11140,7 @@
       <c r="C177" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D177" s="5" t="inlineStr">
+      <c r="D177" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11150,7 +11150,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F177" s="8" t="inlineStr">
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11168,7 +11168,7 @@
       <c r="C178" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D178" s="5" t="inlineStr">
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11206,7 +11206,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F179" s="8" t="inlineStr">
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11224,7 +11224,7 @@
       <c r="C180" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D180" s="5" t="inlineStr">
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11234,7 +11234,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F180" s="8" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11252,7 +11252,7 @@
       <c r="C181" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D181" s="11" t="inlineStr">
+      <c r="D181" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -11308,7 +11308,7 @@
       <c r="C183" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D183" s="5" t="inlineStr">
+      <c r="D183" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11336,7 +11336,7 @@
       <c r="C184" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D184" s="5" t="inlineStr">
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11346,7 +11346,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F184" s="8" t="inlineStr">
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11364,7 +11364,7 @@
       <c r="C185" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D185" s="11" t="inlineStr">
+      <c r="D185" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -11392,7 +11392,7 @@
       <c r="C186" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D186" s="5" t="inlineStr">
+      <c r="D186" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11402,7 +11402,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F186" s="8" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11420,7 +11420,7 @@
       <c r="C187" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D187" s="5" t="inlineStr">
+      <c r="D187" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11448,7 +11448,7 @@
       <c r="C188" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D188" s="5" t="inlineStr">
+      <c r="D188" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11476,7 +11476,7 @@
       <c r="C189" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D189" s="5" t="inlineStr">
+      <c r="D189" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11504,7 +11504,7 @@
       <c r="C190" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D190" s="5" t="inlineStr">
+      <c r="D190" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11542,7 +11542,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F191" s="8" t="inlineStr">
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11560,7 +11560,7 @@
       <c r="C192" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D192" s="11" t="inlineStr">
+      <c r="D192" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -11598,9 +11598,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       <c r="C194" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D194" s="9" t="inlineStr">
+      <c r="D194" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -11626,9 +11626,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F194" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11644,7 @@
       <c r="C195" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D195" s="5" t="inlineStr">
+      <c r="D195" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11672,7 +11672,7 @@
       <c r="C196" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D196" s="5" t="inlineStr">
+      <c r="D196" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11682,7 +11682,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F196" s="8" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11700,7 +11700,7 @@
       <c r="C197" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D197" s="5" t="inlineStr">
+      <c r="D197" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11756,7 +11756,7 @@
       <c r="C199" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="D199" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11784,7 +11784,7 @@
       <c r="C200" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D200" s="5" t="inlineStr">
+      <c r="D200" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11840,7 +11840,7 @@
       <c r="C202" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D202" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11868,7 +11868,7 @@
       <c r="C203" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D203" s="5" t="inlineStr">
+      <c r="D203" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -11924,7 +11924,7 @@
       <c r="C205" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D205" s="9" t="inlineStr">
+      <c r="D205" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -11952,7 +11952,7 @@
       <c r="C206" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D206" s="9" t="inlineStr">
+      <c r="D206" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -11962,7 +11962,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F206" s="8" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -11980,7 +11980,7 @@
       <c r="C207" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D207" s="9" t="inlineStr">
+      <c r="D207" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -11990,7 +11990,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F207" s="8" t="inlineStr">
+      <c r="F207" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12018,7 +12018,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F208" s="8" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12036,7 +12036,7 @@
       <c r="C209" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D209" s="9" t="inlineStr">
+      <c r="D209" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12120,7 +12120,7 @@
       <c r="C212" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D212" s="5" t="inlineStr">
+      <c r="D212" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12130,9 +12130,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F212" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       <c r="C213" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="D213" s="9" t="inlineStr">
+      <c r="D213" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12176,7 +12176,7 @@
       <c r="C214" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D214" s="9" t="inlineStr">
+      <c r="D214" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12204,7 +12204,7 @@
       <c r="C215" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D215" s="11" t="inlineStr">
+      <c r="D215" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -12232,7 +12232,7 @@
       <c r="C216" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D216" s="9" t="inlineStr">
+      <c r="D216" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12260,7 +12260,7 @@
       <c r="C217" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D217" s="5" t="inlineStr">
+      <c r="D217" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12270,7 +12270,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr">
+      <c r="F217" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12288,7 +12288,7 @@
       <c r="C218" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D218" s="9" t="inlineStr">
+      <c r="D218" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12316,7 +12316,7 @@
       <c r="C219" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D219" s="5" t="inlineStr">
+      <c r="D219" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12326,7 +12326,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F219" s="8" t="inlineStr">
+      <c r="F219" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12344,7 +12344,7 @@
       <c r="C220" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D220" s="5" t="inlineStr">
+      <c r="D220" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12354,9 +12354,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F220" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       <c r="C221" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D221" s="5" t="inlineStr">
+      <c r="D221" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12382,7 +12382,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F221" s="8" t="inlineStr">
+      <c r="F221" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12400,7 +12400,7 @@
       <c r="C222" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D222" s="9" t="inlineStr">
+      <c r="D222" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12484,7 +12484,7 @@
       <c r="C225" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D225" s="5" t="inlineStr">
+      <c r="D225" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12494,9 +12494,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F225" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -12512,7 +12512,7 @@
       <c r="C226" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="D226" s="9" t="inlineStr">
+      <c r="D226" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12568,7 +12568,7 @@
       <c r="C228" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D228" s="5" t="inlineStr">
+      <c r="D228" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12578,7 +12578,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F228" s="8" t="inlineStr">
+      <c r="F228" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -12596,7 +12596,7 @@
       <c r="C229" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D229" s="5" t="inlineStr">
+      <c r="D229" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12708,7 +12708,7 @@
       <c r="C233" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D233" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12736,7 +12736,7 @@
       <c r="C234" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D234" s="5" t="inlineStr">
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12764,7 +12764,7 @@
       <c r="C235" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D235" s="5" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12792,7 +12792,7 @@
       <c r="C236" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D236" s="5" t="inlineStr">
+      <c r="D236" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12820,7 +12820,7 @@
       <c r="C237" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D237" s="5" t="inlineStr">
+      <c r="D237" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12848,7 +12848,7 @@
       <c r="C238" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D238" s="5" t="inlineStr">
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12904,7 +12904,7 @@
       <c r="C240" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D240" s="5" t="inlineStr">
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12932,7 +12932,7 @@
       <c r="C241" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D241" s="5" t="inlineStr">
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -12960,7 +12960,7 @@
       <c r="C242" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D242" s="9" t="inlineStr">
+      <c r="D242" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -12988,7 +12988,7 @@
       <c r="C243" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D243" s="5" t="inlineStr">
+      <c r="D243" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13016,7 +13016,7 @@
       <c r="C244" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D244" s="5" t="inlineStr">
+      <c r="D244" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13072,7 +13072,7 @@
       <c r="C246" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D246" s="5" t="inlineStr">
+      <c r="D246" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13100,7 +13100,7 @@
       <c r="C247" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="D247" s="9" t="inlineStr">
+      <c r="D247" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -13156,7 +13156,7 @@
       <c r="C249" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D249" s="5" t="inlineStr">
+      <c r="D249" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13240,7 +13240,7 @@
       <c r="C252" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D252" s="5" t="inlineStr">
+      <c r="D252" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13268,7 +13268,7 @@
       <c r="C253" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D253" s="5" t="inlineStr">
+      <c r="D253" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13296,7 +13296,7 @@
       <c r="C254" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D254" s="5" t="inlineStr">
+      <c r="D254" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13306,7 +13306,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F254" s="8" t="inlineStr">
+      <c r="F254" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -13324,7 +13324,7 @@
       <c r="C255" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D255" s="5" t="inlineStr">
+      <c r="D255" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13352,7 +13352,7 @@
       <c r="C256" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D256" s="5" t="inlineStr">
+      <c r="D256" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13362,7 +13362,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F256" s="8" t="inlineStr">
+      <c r="F256" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -13380,7 +13380,7 @@
       <c r="C257" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D257" s="5" t="inlineStr">
+      <c r="D257" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13408,7 +13408,7 @@
       <c r="C258" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D258" s="11" t="inlineStr">
+      <c r="D258" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -13436,7 +13436,7 @@
       <c r="C259" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D259" s="5" t="inlineStr">
+      <c r="D259" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13446,9 +13446,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F259" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       <c r="C260" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="D260" s="9" t="inlineStr">
+      <c r="D260" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -13492,7 +13492,7 @@
       <c r="C261" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D261" s="5" t="inlineStr">
+      <c r="D261" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13502,7 +13502,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F261" s="8" t="inlineStr">
+      <c r="F261" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -13548,7 +13548,7 @@
       <c r="C263" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D263" s="5" t="inlineStr">
+      <c r="D263" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13604,7 +13604,7 @@
       <c r="C265" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="D265" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13632,7 +13632,7 @@
       <c r="C266" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D266" s="5" t="inlineStr">
+      <c r="D266" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13688,7 +13688,7 @@
       <c r="C268" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D268" s="5" t="inlineStr">
+      <c r="D268" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13698,7 +13698,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F268" s="8" t="inlineStr">
+      <c r="F268" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -13716,7 +13716,7 @@
       <c r="C269" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D269" s="5" t="inlineStr">
+      <c r="D269" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13810,7 +13810,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F272" s="8" t="inlineStr">
+      <c r="F272" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -13856,7 +13856,7 @@
       <c r="C274" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D274" s="5" t="inlineStr">
+      <c r="D274" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13866,9 +13866,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F274" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       <c r="C275" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D275" s="5" t="inlineStr">
+      <c r="D275" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -13940,7 +13940,7 @@
       <c r="C277" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="D277" s="9" t="inlineStr">
+      <c r="D277" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -13968,7 +13968,7 @@
       <c r="C278" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="D278" s="9" t="inlineStr">
+      <c r="D278" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -14024,7 +14024,7 @@
       <c r="C280" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D280" s="5" t="inlineStr">
+      <c r="D280" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14062,7 +14062,7 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F281" s="8" t="inlineStr">
+      <c r="F281" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -14080,7 +14080,7 @@
       <c r="C282" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="D282" s="9" t="inlineStr">
+      <c r="D282" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -14108,7 +14108,7 @@
       <c r="C283" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D283" s="5" t="inlineStr">
+      <c r="D283" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14164,7 +14164,7 @@
       <c r="C285" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D285" s="5" t="inlineStr">
+      <c r="D285" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14192,7 +14192,7 @@
       <c r="C286" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D286" s="5" t="inlineStr">
+      <c r="D286" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14248,7 +14248,7 @@
       <c r="C288" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D288" s="5" t="inlineStr">
+      <c r="D288" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14286,9 +14286,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F289" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F289" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       <c r="C291" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D291" s="5" t="inlineStr">
+      <c r="D291" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14360,7 +14360,7 @@
       <c r="C292" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="D292" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14388,7 +14388,7 @@
       <c r="C293" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D293" s="11" t="inlineStr">
+      <c r="D293" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -14416,7 +14416,7 @@
       <c r="C294" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D294" s="11" t="inlineStr">
+      <c r="D294" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -14426,9 +14426,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F294" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F294" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       <c r="C296" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D296" s="5" t="inlineStr">
+      <c r="D296" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14500,7 +14500,7 @@
       <c r="C297" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="D297" s="9" t="inlineStr">
+      <c r="D297" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -14528,7 +14528,7 @@
       <c r="C298" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D298" s="5" t="inlineStr">
+      <c r="D298" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14556,7 +14556,7 @@
       <c r="C299" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D299" s="5" t="inlineStr">
+      <c r="D299" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14566,7 +14566,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F299" s="8" t="inlineStr">
+      <c r="F299" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -14584,7 +14584,7 @@
       <c r="C300" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D300" s="5" t="inlineStr">
+      <c r="D300" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14594,7 +14594,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F300" s="8" t="inlineStr">
+      <c r="F300" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -14612,7 +14612,7 @@
       <c r="C301" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D301" s="9" t="inlineStr">
+      <c r="D301" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -14640,7 +14640,7 @@
       <c r="C302" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D302" s="5" t="inlineStr">
+      <c r="D302" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14668,7 +14668,7 @@
       <c r="C303" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D303" s="5" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14678,9 +14678,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F303" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F303" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
       <c r="C304" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="D304" s="11" t="inlineStr">
+      <c r="D304" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -14752,7 +14752,7 @@
       <c r="C306" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D306" s="5" t="inlineStr">
+      <c r="D306" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14762,9 +14762,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F306" s="8" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F306" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       <c r="C307" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D307" s="5" t="inlineStr">
+      <c r="D307" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14920,7 +14920,7 @@
       <c r="C312" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D312" s="5" t="inlineStr">
+      <c r="D312" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -14948,7 +14948,7 @@
       <c r="C313" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D313" s="11" t="inlineStr">
+      <c r="D313" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -14976,7 +14976,7 @@
       <c r="C314" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D314" s="5" t="inlineStr">
+      <c r="D314" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15032,7 +15032,7 @@
       <c r="C316" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D316" s="5" t="inlineStr">
+      <c r="D316" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15060,7 +15060,7 @@
       <c r="C317" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D317" s="5" t="inlineStr">
+      <c r="D317" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15070,7 +15070,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F317" s="8" t="inlineStr">
+      <c r="F317" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -15088,7 +15088,7 @@
       <c r="C318" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D318" s="5" t="inlineStr">
+      <c r="D318" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15116,7 +15116,7 @@
       <c r="C319" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D319" s="5" t="inlineStr">
+      <c r="D319" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15126,7 +15126,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F319" s="8" t="inlineStr">
+      <c r="F319" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -15144,7 +15144,7 @@
       <c r="C320" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D320" s="5" t="inlineStr">
+      <c r="D320" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15172,7 +15172,7 @@
       <c r="C321" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D321" s="5" t="inlineStr">
+      <c r="D321" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15200,7 +15200,7 @@
       <c r="C322" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D322" s="5" t="inlineStr">
+      <c r="D322" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15256,7 +15256,7 @@
       <c r="C324" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D324" s="5" t="inlineStr">
+      <c r="D324" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15284,7 +15284,7 @@
       <c r="C325" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D325" s="5" t="inlineStr">
+      <c r="D325" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15312,7 +15312,7 @@
       <c r="C326" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D326" s="5" t="inlineStr">
+      <c r="D326" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15396,7 +15396,7 @@
       <c r="C329" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D329" s="5" t="inlineStr">
+      <c r="D329" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15424,7 +15424,7 @@
       <c r="C330" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D330" s="5" t="inlineStr">
+      <c r="D330" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15452,7 +15452,7 @@
       <c r="C331" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D331" s="5" t="inlineStr">
+      <c r="D331" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15508,7 +15508,7 @@
       <c r="C333" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="D333" s="9" t="inlineStr">
+      <c r="D333" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -15536,7 +15536,7 @@
       <c r="C334" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D334" s="5" t="inlineStr">
+      <c r="D334" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15564,7 +15564,7 @@
       <c r="C335" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D335" s="5" t="inlineStr">
+      <c r="D335" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15592,7 +15592,7 @@
       <c r="C336" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D336" s="5" t="inlineStr">
+      <c r="D336" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15676,7 +15676,7 @@
       <c r="C339" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D339" s="5" t="inlineStr">
+      <c r="D339" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15704,7 +15704,7 @@
       <c r="C340" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D340" s="5" t="inlineStr">
+      <c r="D340" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15732,7 +15732,7 @@
       <c r="C341" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D341" s="5" t="inlineStr">
+      <c r="D341" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15760,7 +15760,7 @@
       <c r="C342" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D342" s="5" t="inlineStr">
+      <c r="D342" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15788,7 +15788,7 @@
       <c r="C343" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D343" s="5" t="inlineStr">
+      <c r="D343" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15816,7 +15816,7 @@
       <c r="C344" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D344" s="5" t="inlineStr">
+      <c r="D344" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -15854,7 +15854,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F345" s="8" t="inlineStr">
+      <c r="F345" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -15872,7 +15872,7 @@
       <c r="C346" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="D346" s="9" t="inlineStr">
+      <c r="D346" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -15928,7 +15928,7 @@
       <c r="C348" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D348" s="5" t="inlineStr">
+      <c r="D348" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16012,7 +16012,7 @@
       <c r="C351" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D351" s="5" t="inlineStr">
+      <c r="D351" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16068,7 +16068,7 @@
       <c r="C353" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="D353" s="5" t="inlineStr">
+      <c r="D353" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16096,7 +16096,7 @@
       <c r="C354" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D354" s="5" t="inlineStr">
+      <c r="D354" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16124,7 +16124,7 @@
       <c r="C355" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D355" s="5" t="inlineStr">
+      <c r="D355" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16152,7 +16152,7 @@
       <c r="C356" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D356" s="5" t="inlineStr">
+      <c r="D356" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16180,7 +16180,7 @@
       <c r="C357" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D357" s="5" t="inlineStr">
+      <c r="D357" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16208,7 +16208,7 @@
       <c r="C358" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D358" s="11" t="inlineStr">
+      <c r="D358" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -16236,7 +16236,7 @@
       <c r="C359" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D359" s="5" t="inlineStr">
+      <c r="D359" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16330,9 +16330,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F362" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F362" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -16348,7 +16348,7 @@
       <c r="C363" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D363" s="5" t="inlineStr">
+      <c r="D363" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16358,7 +16358,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F363" s="8" t="inlineStr">
+      <c r="F363" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -16432,7 +16432,7 @@
       <c r="C366" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D366" s="9" t="inlineStr">
+      <c r="D366" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16442,9 +16442,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F366" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F366" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -16460,7 +16460,7 @@
       <c r="C367" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D367" s="9" t="inlineStr">
+      <c r="D367" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16516,7 +16516,7 @@
       <c r="C369" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D369" s="5" t="inlineStr">
+      <c r="D369" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16544,7 +16544,7 @@
       <c r="C370" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="D370" s="9" t="inlineStr">
+      <c r="D370" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16572,7 +16572,7 @@
       <c r="C371" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="D371" s="9" t="inlineStr">
+      <c r="D371" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16628,7 +16628,7 @@
       <c r="C373" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="D373" s="9" t="inlineStr">
+      <c r="D373" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16656,7 +16656,7 @@
       <c r="C374" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D374" s="5" t="inlineStr">
+      <c r="D374" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16684,7 +16684,7 @@
       <c r="C375" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D375" s="5" t="inlineStr">
+      <c r="D375" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16768,7 +16768,7 @@
       <c r="C378" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D378" s="5" t="inlineStr">
+      <c r="D378" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16796,7 +16796,7 @@
       <c r="C379" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="D379" s="9" t="inlineStr">
+      <c r="D379" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -16824,7 +16824,7 @@
       <c r="C380" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D380" s="5" t="inlineStr">
+      <c r="D380" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -16992,7 +16992,7 @@
       <c r="C386" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D386" s="5" t="inlineStr">
+      <c r="D386" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17048,7 +17048,7 @@
       <c r="C388" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D388" s="5" t="inlineStr">
+      <c r="D388" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17076,7 +17076,7 @@
       <c r="C389" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="D389" s="9" t="inlineStr">
+      <c r="D389" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -17104,7 +17104,7 @@
       <c r="C390" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D390" s="5" t="inlineStr">
+      <c r="D390" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17132,7 +17132,7 @@
       <c r="C391" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D391" s="11" t="inlineStr">
+      <c r="D391" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -17160,7 +17160,7 @@
       <c r="C392" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D392" s="5" t="inlineStr">
+      <c r="D392" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17188,7 +17188,7 @@
       <c r="C393" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="D393" s="11" t="inlineStr">
+      <c r="D393" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -17216,7 +17216,7 @@
       <c r="C394" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="D394" s="5" t="inlineStr">
+      <c r="D394" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17244,7 +17244,7 @@
       <c r="C395" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D395" s="5" t="inlineStr">
+      <c r="D395" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17272,7 +17272,7 @@
       <c r="C396" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D396" s="5" t="inlineStr">
+      <c r="D396" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17282,7 +17282,7 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F396" s="8" t="inlineStr">
+      <c r="F396" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -17300,7 +17300,7 @@
       <c r="C397" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D397" s="5" t="inlineStr">
+      <c r="D397" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17328,7 +17328,7 @@
       <c r="C398" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D398" s="11" t="inlineStr">
+      <c r="D398" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -17338,9 +17338,9 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="F398" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F398" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -17384,7 +17384,7 @@
       <c r="C400" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D400" s="5" t="inlineStr">
+      <c r="D400" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17440,7 +17440,7 @@
       <c r="C402" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D402" s="11" t="inlineStr">
+      <c r="D402" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -17468,7 +17468,7 @@
       <c r="C403" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D403" s="11" t="inlineStr">
+      <c r="D403" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -17496,7 +17496,7 @@
       <c r="C404" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="D404" s="9" t="inlineStr">
+      <c r="D404" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -17524,7 +17524,7 @@
       <c r="C405" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D405" s="5" t="inlineStr">
+      <c r="D405" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17608,7 +17608,7 @@
       <c r="C408" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D408" s="5" t="inlineStr">
+      <c r="D408" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17636,7 +17636,7 @@
       <c r="C409" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D409" s="5" t="inlineStr">
+      <c r="D409" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17664,7 +17664,7 @@
       <c r="C410" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D410" s="5" t="inlineStr">
+      <c r="D410" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17674,7 +17674,7 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F410" s="8" t="inlineStr">
+      <c r="F410" s="7" t="inlineStr">
         <is>
           <t>Yes (planned)</t>
         </is>
@@ -17720,7 +17720,7 @@
       <c r="C412" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D412" s="5" t="inlineStr">
+      <c r="D412" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17776,7 +17776,7 @@
       <c r="C414" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D414" s="5" t="inlineStr">
+      <c r="D414" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17804,7 +17804,7 @@
       <c r="C415" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D415" s="5" t="inlineStr">
+      <c r="D415" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17832,7 +17832,7 @@
       <c r="C416" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="D416" s="5" t="inlineStr">
+      <c r="D416" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17860,7 +17860,7 @@
       <c r="C417" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D417" s="5" t="inlineStr">
+      <c r="D417" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17888,7 +17888,7 @@
       <c r="C418" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D418" s="5" t="inlineStr">
+      <c r="D418" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17916,7 +17916,7 @@
       <c r="C419" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D419" s="5" t="inlineStr">
+      <c r="D419" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17944,7 +17944,7 @@
       <c r="C420" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D420" s="5" t="inlineStr">
+      <c r="D420" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -17972,7 +17972,7 @@
       <c r="C421" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D421" s="5" t="inlineStr">
+      <c r="D421" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18000,7 +18000,7 @@
       <c r="C422" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="D422" s="5" t="inlineStr">
+      <c r="D422" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18056,7 +18056,7 @@
       <c r="C424" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D424" s="11" t="inlineStr">
+      <c r="D424" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18084,7 +18084,7 @@
       <c r="C425" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D425" s="5" t="inlineStr">
+      <c r="D425" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18112,7 +18112,7 @@
       <c r="C426" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D426" s="5" t="inlineStr">
+      <c r="D426" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18140,7 +18140,7 @@
       <c r="C427" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="D427" s="9" t="inlineStr">
+      <c r="D427" s="10" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -18168,7 +18168,7 @@
       <c r="C428" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D428" s="11" t="inlineStr">
+      <c r="D428" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18196,7 +18196,7 @@
       <c r="C429" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D429" s="11" t="inlineStr">
+      <c r="D429" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18224,7 +18224,7 @@
       <c r="C430" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D430" s="11" t="inlineStr">
+      <c r="D430" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18252,7 +18252,7 @@
       <c r="C431" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="D431" s="5" t="inlineStr">
+      <c r="D431" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18308,7 +18308,7 @@
       <c r="C433" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D433" s="5" t="inlineStr">
+      <c r="D433" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18336,7 +18336,7 @@
       <c r="C434" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="D434" s="5" t="inlineStr">
+      <c r="D434" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18364,7 +18364,7 @@
       <c r="C435" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="D435" s="5" t="inlineStr">
+      <c r="D435" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18392,7 +18392,7 @@
       <c r="C436" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D436" s="11" t="inlineStr">
+      <c r="D436" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18420,7 +18420,7 @@
       <c r="C437" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="D437" s="11" t="inlineStr">
+      <c r="D437" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18448,7 +18448,7 @@
       <c r="C438" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D438" s="5" t="inlineStr">
+      <c r="D438" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18476,7 +18476,7 @@
       <c r="C439" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="D439" s="5" t="inlineStr">
+      <c r="D439" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18532,7 +18532,7 @@
       <c r="C441" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D441" s="5" t="inlineStr">
+      <c r="D441" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18560,7 +18560,7 @@
       <c r="C442" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D442" s="5" t="inlineStr">
+      <c r="D442" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18616,7 +18616,7 @@
       <c r="C444" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="D444" s="5" t="inlineStr">
+      <c r="D444" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18644,7 +18644,7 @@
       <c r="C445" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D445" s="5" t="inlineStr">
+      <c r="D445" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18672,7 +18672,7 @@
       <c r="C446" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="D446" s="5" t="inlineStr">
+      <c r="D446" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18700,7 +18700,7 @@
       <c r="C447" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="D447" s="5" t="inlineStr">
+      <c r="D447" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
@@ -18756,7 +18756,7 @@
       <c r="C449" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D449" s="11" t="inlineStr">
+      <c r="D449" s="12" t="inlineStr">
         <is>
           <t>Very Easy</t>
         </is>
@@ -18794,9 +18794,9 @@
           <t>Transactional</t>
         </is>
       </c>
-      <c r="F450" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F450" s="7" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -18812,7 +18812,7 @@
       <c r="C451" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="D451" s="5" t="inlineStr">
+      <c r="D451" s="8" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>

--- a/decks/girlievault/keyword-research.xlsx
+++ b/decks/girlievault/keyword-research.xlsx
@@ -21729,9 +21729,9 @@
     <row r="14" ht="65" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>BoFu (48) — category buying guides for shoppers ready to purchase.
-MoFu (54) — best-of, comparison and use-case articles that capture consideration (and feed AI 'best brand' answers).
-ToFu (18) — education and styling that builds topical authority and earns citations.
+          <t>BoFu (53) — category buying guides for shoppers ready to purchase.
+MoFu (48) — best-of, comparison and use-case articles that capture consideration (and feed AI 'best brand' answers).
+ToFu (19) — education and styling that builds topical authority and earns citations.
 The MoFu/ToFu weighting is deliberate: those terms are winnable at a young domain and are exactly what AI engines cite when shoppers ask for recommendations.</t>
         </is>
       </c>
